--- a/资源规划.xlsx
+++ b/资源规划.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27526" windowHeight="14964" activeTab="1"/>
+    <workbookView windowWidth="27526" windowHeight="14964"/>
   </bookViews>
   <sheets>
     <sheet name="引脚分配" sheetId="1" r:id="rId1"/>

--- a/资源规划.xlsx
+++ b/资源规划.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27526" windowHeight="14964"/>
+    <workbookView windowWidth="22192" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="引脚分配" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
   <si>
     <t>引脚</t>
   </si>
@@ -94,6 +94,9 @@
     <t>PA3</t>
   </si>
   <si>
+    <t>陀螺仪</t>
+  </si>
+  <si>
     <t>步进电机扩展板</t>
   </si>
   <si>
@@ -103,9 +106,18 @@
     <t>USART3</t>
   </si>
   <si>
+    <t>激光测量</t>
+  </si>
+  <si>
+    <t>5-24v</t>
+  </si>
+  <si>
     <t>PB11</t>
   </si>
   <si>
+    <t>jeston</t>
+  </si>
+  <si>
     <t>总线舵机</t>
   </si>
   <si>
@@ -148,7 +160,43 @@
     <t>PC7</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>PG7-PG10</t>
+  </si>
+  <si>
+    <t>GPIO INPUT（每个1个）</t>
+  </si>
+  <si>
+    <t>VCC+GND+GPIO</t>
+  </si>
+  <si>
+    <t>7.4v</t>
+  </si>
+  <si>
+    <t>额外空闲gpio</t>
+  </si>
+  <si>
+    <t>PCO-PC3</t>
+  </si>
+  <si>
+    <t>4个</t>
+  </si>
+  <si>
+    <t>PE0-PE1</t>
+  </si>
+  <si>
+    <t>2个</t>
+  </si>
+  <si>
+    <t>通用/PWM执行器</t>
+  </si>
+  <si>
+    <t>PA4-PA5</t>
+  </si>
+  <si>
+    <t>PG11-PG14</t>
+  </si>
+  <si>
+    <t>通用开关/传感器</t>
   </si>
   <si>
     <t>id</t>
@@ -899,7 +947,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="155575" y="167640"/>
-          <a:ext cx="2667635" cy="3558540"/>
+          <a:ext cx="2712085" cy="3364230"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1161,13 +1209,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F4:O17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="F4:O23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="6" max="6" width="21.8468468468468" customWidth="1"/>
-    <col min="10" max="10" width="11.7747747747748" customWidth="1"/>
-    <col min="13" max="13" width="24.8378378378378" customWidth="1"/>
-    <col min="15" max="15" width="33.7207207207207" customWidth="1"/>
+    <col min="6" max="6" width="24.0088495575221" customWidth="1"/>
+    <col min="7" max="7" width="10.5663716814159" customWidth="1"/>
+    <col min="8" max="8" width="18.3008849557522" customWidth="1"/>
+    <col min="9" max="9" width="16.5132743362832" customWidth="1"/>
+    <col min="10" max="10" width="11.7787610619469" customWidth="1"/>
+    <col min="13" max="13" width="24.8407079646018" customWidth="1"/>
+    <col min="15" max="15" width="33.716814159292" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="6:15">
@@ -1251,6 +1302,9 @@
       <c r="N7" t="s">
         <v>19</v>
       </c>
+      <c r="O7">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="8" spans="6:15">
       <c r="F8" s="1"/>
@@ -1261,52 +1315,73 @@
         <v>12</v>
       </c>
       <c r="I8" s="1"/>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="6:15">
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9">
         <v>12</v>
+      </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9">
+        <v>7.4</v>
       </c>
     </row>
     <row r="10" spans="6:15">
       <c r="F10" s="1"/>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
       </c>
       <c r="I10" s="1"/>
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="6:15">
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
         <v>6</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="6:15">
       <c r="F12" s="1"/>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H12" t="s">
         <v>12</v>
@@ -1315,16 +1390,16 @@
     </row>
     <row r="13" spans="6:15">
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
         <v>6</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1333,7 +1408,7 @@
     <row r="14" spans="6:15">
       <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
         <v>12</v>
@@ -1342,37 +1417,90 @@
     </row>
     <row r="15" spans="6:15">
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
         <v>6</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K15" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="6:15">
       <c r="F16" s="1"/>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H16" t="s">
         <v>12</v>
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="10:10">
+    <row r="17" spans="6:10">
+      <c r="F17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="6:10">
+      <c r="F20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="6:10">
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="6:10">
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="6:10">
+      <c r="G23" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1400,24 +1528,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="34.8288288288288" customWidth="1"/>
+    <col min="1" max="1" width="34.8318584070796" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1"/>
     <row r="4" spans="3:7">
       <c r="C4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="3:7">
@@ -1425,13 +1553,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="3:7">
@@ -1439,13 +1567,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="3:7">
@@ -1453,13 +1581,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="3:7">
@@ -1467,7 +1595,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="3:7">
@@ -1475,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="3:7">
@@ -1483,7 +1611,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1498,7 +1626,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/资源规划.xlsx
+++ b/资源规划.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22192" windowHeight="10455"/>
+    <workbookView windowWidth="27526" windowHeight="14964"/>
   </bookViews>
   <sheets>
     <sheet name="引脚分配" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>引脚</t>
   </si>
@@ -170,6 +170,36 @@
   </si>
   <si>
     <t>7.4v</t>
+  </si>
+  <si>
+    <t>替换为PCO-PC3</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>PC0</t>
+  </si>
+  <si>
+    <t>丝杆上限位</t>
+  </si>
+  <si>
+    <t>PC1</t>
+  </si>
+  <si>
+    <t>丝杆下限位</t>
+  </si>
+  <si>
+    <t>PC2</t>
+  </si>
+  <si>
+    <t>机械臂平移前限位</t>
+  </si>
+  <si>
+    <t>PC3</t>
+  </si>
+  <si>
+    <t>机械臂平移后限位</t>
   </si>
   <si>
     <t>额外空闲gpio</t>
@@ -245,8 +275,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -398,12 +436,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -718,55 +762,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
@@ -781,79 +822,91 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -947,7 +1000,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="155575" y="167640"/>
-          <a:ext cx="2712085" cy="3364230"/>
+          <a:ext cx="2667635" cy="3558540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1209,16 +1262,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F4:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="F4:O29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="6" max="6" width="24.0088495575221" customWidth="1"/>
-    <col min="7" max="7" width="10.5663716814159" customWidth="1"/>
-    <col min="8" max="8" width="18.3008849557522" customWidth="1"/>
-    <col min="9" max="9" width="16.5132743362832" customWidth="1"/>
-    <col min="10" max="10" width="11.7787610619469" customWidth="1"/>
-    <col min="13" max="13" width="24.8407079646018" customWidth="1"/>
-    <col min="15" max="15" width="33.716814159292" customWidth="1"/>
+    <col min="6" max="6" width="24.009009009009" customWidth="1"/>
+    <col min="7" max="7" width="10.5675675675676" customWidth="1"/>
+    <col min="8" max="8" width="24.4684684684685" customWidth="1"/>
+    <col min="9" max="9" width="16.5135135135135" customWidth="1"/>
+    <col min="10" max="10" width="11.7747747747748" customWidth="1"/>
+    <col min="13" max="13" width="24.8378378378378" customWidth="1"/>
+    <col min="15" max="15" width="33.7207207207207" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="6:15">
@@ -1449,7 +1502,7 @@
       <c r="F17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="H17" t="s">
@@ -1462,45 +1515,90 @@
         <v>46</v>
       </c>
     </row>
+    <row r="18" spans="6:10">
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="6:10">
+      <c r="H19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="20" spans="6:10">
-      <c r="F20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="H20" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="I20" s="4" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="21" spans="6:10">
-      <c r="G21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="H21" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="6:10">
-      <c r="G22" t="s">
+    <row r="22" ht="28.8" spans="6:10">
+      <c r="H22" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="6:10">
-      <c r="G23" t="s">
+      <c r="I22" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H23" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" t="s">
+    </row>
+    <row r="23" ht="28.8" spans="6:10">
+      <c r="H23" s="4" t="s">
         <v>55</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="6:10">
+      <c r="F26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="6:10">
+      <c r="G27" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="6:10">
+      <c r="G28" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="6:10">
+      <c r="G29" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1528,24 +1626,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="34.8318584070796" customWidth="1"/>
+    <col min="1" max="1" width="34.8288288288288" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1"/>
     <row r="4" spans="3:7">
       <c r="C4" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="3:7">
@@ -1553,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="3:7">
@@ -1567,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="3:7">
@@ -1581,13 +1679,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="3:7">
@@ -1595,7 +1693,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="3:7">
@@ -1603,7 +1701,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="3:7">
@@ -1611,7 +1709,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1724,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
